--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/139.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/139.xlsx
@@ -426,13 +426,13 @@
         <v>-6.597040251074097</v>
       </c>
       <c r="E2">
-        <v>-14.73192050661062</v>
+        <v>-15.9315766698786</v>
       </c>
       <c r="F2">
-        <v>-0.474387934747923</v>
+        <v>0.2359089486609579</v>
       </c>
       <c r="G2">
-        <v>-8.766282701566427</v>
+        <v>-11.5805973277741</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.43242692960551</v>
       </c>
       <c r="E3">
-        <v>-14.54901544144081</v>
+        <v>-16.02388055557695</v>
       </c>
       <c r="F3">
-        <v>-0.6508500723618849</v>
+        <v>0.1374251765095274</v>
       </c>
       <c r="G3">
-        <v>-9.247808171344499</v>
+        <v>-11.68492254935315</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.166876231205118</v>
       </c>
       <c r="E4">
-        <v>-15.85581982820428</v>
+        <v>-16.05389075282578</v>
       </c>
       <c r="F4">
-        <v>-0.5945608506068529</v>
+        <v>0.660994793448955</v>
       </c>
       <c r="G4">
-        <v>-9.038839915814624</v>
+        <v>-11.77404905636141</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.800819038028409</v>
       </c>
       <c r="E5">
-        <v>-17.04029654659856</v>
+        <v>-18.03177423125993</v>
       </c>
       <c r="F5">
-        <v>-0.1027417278493276</v>
+        <v>0.1052720957698646</v>
       </c>
       <c r="G5">
-        <v>-8.959347096325644</v>
+        <v>-12.51688912773631</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.344705109031301</v>
       </c>
       <c r="E6">
-        <v>-17.47331375968601</v>
+        <v>-17.89447089934736</v>
       </c>
       <c r="F6">
-        <v>-0.2595823267931776</v>
+        <v>0.3659535188590494</v>
       </c>
       <c r="G6">
-        <v>-8.704782697083386</v>
+        <v>-12.06395352923539</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.80851813513855</v>
       </c>
       <c r="E7">
-        <v>-17.93609663242587</v>
+        <v>-19.05698451880444</v>
       </c>
       <c r="F7">
-        <v>0.02041579576188886</v>
+        <v>0.07303369318771347</v>
       </c>
       <c r="G7">
-        <v>-7.7029420954436</v>
+        <v>-11.38415286601928</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.214788385577716</v>
       </c>
       <c r="E8">
-        <v>-19.02262698650824</v>
+        <v>-20.46201150679428</v>
       </c>
       <c r="F8">
-        <v>-0.1990618043446457</v>
+        <v>0.7371499222579248</v>
       </c>
       <c r="G8">
-        <v>-8.142271351778122</v>
+        <v>-11.7643955055689</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.581201488261461</v>
       </c>
       <c r="E9">
-        <v>-19.2699722368072</v>
+        <v>-20.84865261756918</v>
       </c>
       <c r="F9">
-        <v>0.4391911376753593</v>
+        <v>0.9055835230039537</v>
       </c>
       <c r="G9">
-        <v>-7.838979032743332</v>
+        <v>-10.9608102340939</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.937644672670843</v>
       </c>
       <c r="E10">
-        <v>-20.63089188796233</v>
+        <v>-20.86239200770845</v>
       </c>
       <c r="F10">
-        <v>0.1018360277830523</v>
+        <v>1.399757694287638</v>
       </c>
       <c r="G10">
-        <v>-7.967964508044416</v>
+        <v>-10.83203663370733</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.306430129120404</v>
       </c>
       <c r="E11">
-        <v>-20.83320599272901</v>
+        <v>-22.27197464055001</v>
       </c>
       <c r="F11">
-        <v>-0.09365785091022825</v>
+        <v>1.095746857460219</v>
       </c>
       <c r="G11">
-        <v>-6.848715408854377</v>
+        <v>-10.03296363580237</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.715435045857971</v>
       </c>
       <c r="E12">
-        <v>-20.70946996894343</v>
+        <v>-22.09887372160681</v>
       </c>
       <c r="F12">
-        <v>0.1422719541833073</v>
+        <v>1.305182987910019</v>
       </c>
       <c r="G12">
-        <v>-6.079467115712706</v>
+        <v>-8.985970503552462</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.175602684888928</v>
       </c>
       <c r="E13">
-        <v>-23.15960083079348</v>
+        <v>-23.07382247614018</v>
       </c>
       <c r="F13">
-        <v>0.3681669165593297</v>
+        <v>1.506554133326162</v>
       </c>
       <c r="G13">
-        <v>-5.967521018302251</v>
+        <v>-8.288296204969836</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.6934766024651555</v>
       </c>
       <c r="E14">
-        <v>-24.61123034479625</v>
+        <v>-23.65794128144157</v>
       </c>
       <c r="F14">
-        <v>0.6214294811890422</v>
+        <v>1.11834472020859</v>
       </c>
       <c r="G14">
-        <v>-5.231739030017073</v>
+        <v>-8.343840538027727</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.2561194562311003</v>
       </c>
       <c r="E15">
-        <v>-24.39301223931463</v>
+        <v>-26.75301288299002</v>
       </c>
       <c r="F15">
-        <v>0.9302009454803495</v>
+        <v>1.79293234161759</v>
       </c>
       <c r="G15">
-        <v>-5.20917104107586</v>
+        <v>-7.21090895412388</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.1506610842567954</v>
       </c>
       <c r="E16">
-        <v>-25.91684374289571</v>
+        <v>-26.15254175804694</v>
       </c>
       <c r="F16">
-        <v>1.087430048736112</v>
+        <v>2.085488513999097</v>
       </c>
       <c r="G16">
-        <v>-5.053426426180848</v>
+        <v>-7.145671343727003</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.5471205266589982</v>
       </c>
       <c r="E17">
-        <v>-26.72037164234273</v>
+        <v>-26.76555675599127</v>
       </c>
       <c r="F17">
-        <v>1.040088851666121</v>
+        <v>1.94254709170682</v>
       </c>
       <c r="G17">
-        <v>-4.189129060061162</v>
+        <v>-6.822727626371099</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.942873491669471</v>
       </c>
       <c r="E18">
-        <v>-27.02183215703334</v>
+        <v>-28.96294895499922</v>
       </c>
       <c r="F18">
-        <v>1.066606548964538</v>
+        <v>1.923214653260285</v>
       </c>
       <c r="G18">
-        <v>-2.372053377193689</v>
+        <v>-5.238727591650474</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.340779181549076</v>
       </c>
       <c r="E19">
-        <v>-29.3200644152441</v>
+        <v>-28.11693491241224</v>
       </c>
       <c r="F19">
-        <v>1.16688373654303</v>
+        <v>2.086297000584229</v>
       </c>
       <c r="G19">
-        <v>-4.280844413681131</v>
+        <v>-5.602596272962849</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.730050318062862</v>
       </c>
       <c r="E20">
-        <v>-28.52695200601473</v>
+        <v>-29.40474687918754</v>
       </c>
       <c r="F20">
-        <v>0.9954928641690065</v>
+        <v>2.103242084175896</v>
       </c>
       <c r="G20">
-        <v>-3.794644453601607</v>
+        <v>-4.714211377499426</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.094432512315063</v>
       </c>
       <c r="E21">
-        <v>-28.19753269280076</v>
+        <v>-29.59480693328947</v>
       </c>
       <c r="F21">
-        <v>1.45408202856323</v>
+        <v>2.721035179714156</v>
       </c>
       <c r="G21">
-        <v>-1.833126358310193</v>
+        <v>-5.712963240151072</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.414033841117552</v>
       </c>
       <c r="E22">
-        <v>-30.17944651310173</v>
+        <v>-30.8164533663387</v>
       </c>
       <c r="F22">
-        <v>1.457228167959062</v>
+        <v>2.268299259388114</v>
       </c>
       <c r="G22">
-        <v>-2.543327761213424</v>
+        <v>-4.631414633562254</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.671711943345634</v>
       </c>
       <c r="E23">
-        <v>-30.62387548068851</v>
+        <v>-31.03233930770637</v>
       </c>
       <c r="F23">
-        <v>1.434042164354704</v>
+        <v>2.296771903757139</v>
       </c>
       <c r="G23">
-        <v>-2.273011786295313</v>
+        <v>-4.282830741004694</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.855746271002441</v>
       </c>
       <c r="E24">
-        <v>-31.38440099095869</v>
+        <v>-31.67689512711412</v>
       </c>
       <c r="F24">
-        <v>1.600267337604869</v>
+        <v>2.019752590382539</v>
       </c>
       <c r="G24">
-        <v>-1.786381455295684</v>
+        <v>-4.126791487556686</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.961078378466275</v>
       </c>
       <c r="E25">
-        <v>-30.38645664541437</v>
+        <v>-31.77658495391898</v>
       </c>
       <c r="F25">
-        <v>1.425915880133241</v>
+        <v>2.460185598042203</v>
       </c>
       <c r="G25">
-        <v>-1.935193787831463</v>
+        <v>-3.134329661429655</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.990542758505579</v>
       </c>
       <c r="E26">
-        <v>-32.28823232543861</v>
+        <v>-32.01829225407838</v>
       </c>
       <c r="F26">
-        <v>1.452047558221954</v>
+        <v>2.032827541468327</v>
       </c>
       <c r="G26">
-        <v>-1.667380585341042</v>
+        <v>-4.258753143297574</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.951694012254347</v>
       </c>
       <c r="E27">
-        <v>-31.1135393751379</v>
+        <v>-31.93216294268949</v>
       </c>
       <c r="F27">
-        <v>1.634298327246679</v>
+        <v>2.282805629345939</v>
       </c>
       <c r="G27">
-        <v>-2.134753472938731</v>
+        <v>-4.074825854226746</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.855912229435189</v>
       </c>
       <c r="E28">
-        <v>-30.6631871635491</v>
+        <v>-32.8650353809806</v>
       </c>
       <c r="F28">
-        <v>1.285239214320218</v>
+        <v>2.053566547764815</v>
       </c>
       <c r="G28">
-        <v>-1.44721937534289</v>
+        <v>-3.162221007598015</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.713570645068269</v>
       </c>
       <c r="E29">
-        <v>-29.51189510268303</v>
+        <v>-32.13466045065348</v>
       </c>
       <c r="F29">
-        <v>0.8633599797484574</v>
+        <v>2.265857232284661</v>
       </c>
       <c r="G29">
-        <v>-1.948992141639146</v>
+        <v>-3.712268148947922</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.534785488543075</v>
       </c>
       <c r="E30">
-        <v>-30.10024123847057</v>
+        <v>-31.6013126316891</v>
       </c>
       <c r="F30">
-        <v>0.8455848720191856</v>
+        <v>2.133961260941313</v>
       </c>
       <c r="G30">
-        <v>-2.163886273684317</v>
+        <v>-3.922789050335716</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.326792070724572</v>
       </c>
       <c r="E31">
-        <v>-28.93222778733119</v>
+        <v>-30.79896439972108</v>
       </c>
       <c r="F31">
-        <v>1.416429416636381</v>
+        <v>2.233524395818591</v>
       </c>
       <c r="G31">
-        <v>-2.260895189621581</v>
+        <v>-4.550326131123345</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.095667089381583</v>
       </c>
       <c r="E32">
-        <v>-29.24384566922101</v>
+        <v>-32.21195697349041</v>
       </c>
       <c r="F32">
-        <v>1.067282496765223</v>
+        <v>1.736952929271205</v>
       </c>
       <c r="G32">
-        <v>-2.570073658625195</v>
+        <v>-4.520921865643539</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.84376781900728</v>
       </c>
       <c r="E33">
-        <v>-29.11156441498295</v>
+        <v>-31.06362427038836</v>
       </c>
       <c r="F33">
-        <v>1.331556549280349</v>
+        <v>1.466537360831723</v>
       </c>
       <c r="G33">
-        <v>-2.09142174237521</v>
+        <v>-4.481966676282934</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.57356002690515</v>
       </c>
       <c r="E34">
-        <v>-29.26993420797919</v>
+        <v>-30.33355954053077</v>
       </c>
       <c r="F34">
-        <v>1.305971593677484</v>
+        <v>1.412771346185618</v>
       </c>
       <c r="G34">
-        <v>-2.583934912798124</v>
+        <v>-5.745790609718485</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.286832559484358</v>
       </c>
       <c r="E35">
-        <v>-28.25661569317883</v>
+        <v>-29.44145468949372</v>
       </c>
       <c r="F35">
-        <v>1.180636292164307</v>
+        <v>2.078463958423357</v>
       </c>
       <c r="G35">
-        <v>-2.470985720089269</v>
+        <v>-5.476034116996511</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.9876837866442014</v>
       </c>
       <c r="E36">
-        <v>-27.71711594227502</v>
+        <v>-29.32366908055421</v>
       </c>
       <c r="F36">
-        <v>1.498782390353097</v>
+        <v>2.195199149560669</v>
       </c>
       <c r="G36">
-        <v>-3.740917610044775</v>
+        <v>-5.215815305973178</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.6803489303127119</v>
       </c>
       <c r="E37">
-        <v>-26.63371929220596</v>
+        <v>-29.30839000925233</v>
       </c>
       <c r="F37">
-        <v>1.503427874747996</v>
+        <v>2.231185086273085</v>
       </c>
       <c r="G37">
-        <v>-3.343334332960463</v>
+        <v>-5.949276601835328</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.3699410291309784</v>
       </c>
       <c r="E38">
-        <v>-26.7339344219957</v>
+        <v>-27.78523777677241</v>
       </c>
       <c r="F38">
-        <v>1.407696767476069</v>
+        <v>2.381454246610526</v>
       </c>
       <c r="G38">
-        <v>-3.803155866183074</v>
+        <v>-5.404003267153048</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.06126537137709059</v>
       </c>
       <c r="E39">
-        <v>-24.8547354491367</v>
+        <v>-28.06434574376116</v>
       </c>
       <c r="F39">
-        <v>1.798361461575538</v>
+        <v>2.664759211837568</v>
       </c>
       <c r="G39">
-        <v>-3.949068160826451</v>
+        <v>-5.334826107564438</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.2401369012712307</v>
       </c>
       <c r="E40">
-        <v>-24.54461196366941</v>
+        <v>-27.48276741237808</v>
       </c>
       <c r="F40">
-        <v>2.047582421646991</v>
+        <v>2.381682876013699</v>
       </c>
       <c r="G40">
-        <v>-4.279354668188459</v>
+        <v>-5.959241343908534</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.5286201671338681</v>
       </c>
       <c r="E41">
-        <v>-25.74102573954791</v>
+        <v>-26.88033092971567</v>
       </c>
       <c r="F41">
-        <v>1.771384848735969</v>
+        <v>2.752103927523554</v>
       </c>
       <c r="G41">
-        <v>-4.718260174693954</v>
+        <v>-7.154685959230438</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.7988547078974249</v>
       </c>
       <c r="E42">
-        <v>-23.64124932624929</v>
+        <v>-25.79104273496263</v>
       </c>
       <c r="F42">
-        <v>2.171441572448379</v>
+        <v>2.751790804645296</v>
       </c>
       <c r="G42">
-        <v>-4.246719310262324</v>
+        <v>-6.271829674817598</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.046636747882272</v>
       </c>
       <c r="E43">
-        <v>-23.20320550701333</v>
+        <v>-25.94775057799806</v>
       </c>
       <c r="F43">
-        <v>2.315574187065882</v>
+        <v>3.126696637273907</v>
       </c>
       <c r="G43">
-        <v>-4.934508319864688</v>
+        <v>-6.322487642659525</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.270583715736674</v>
       </c>
       <c r="E44">
-        <v>-23.67675709094344</v>
+        <v>-24.33334959426358</v>
       </c>
       <c r="F44">
-        <v>2.250568883498593</v>
+        <v>2.726629973152664</v>
       </c>
       <c r="G44">
-        <v>-5.284999086652867</v>
+        <v>-6.889435118987413</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.471449157719696</v>
       </c>
       <c r="E45">
-        <v>-22.37441777955152</v>
+        <v>-23.32454596804886</v>
       </c>
       <c r="F45">
-        <v>2.253194808165468</v>
+        <v>3.260232776074799</v>
       </c>
       <c r="G45">
-        <v>-5.17197375139661</v>
+        <v>-7.044444792772707</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.652465465642994</v>
       </c>
       <c r="E46">
-        <v>-20.99050706585945</v>
+        <v>-23.09094463636318</v>
       </c>
       <c r="F46">
-        <v>2.397655456274479</v>
+        <v>3.091101689975613</v>
       </c>
       <c r="G46">
-        <v>-5.162138120599435</v>
+        <v>-6.522140023041892</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.817385313290609</v>
       </c>
       <c r="E47">
-        <v>-21.41175024652695</v>
+        <v>-21.75886230768889</v>
       </c>
       <c r="F47">
-        <v>2.575421444180447</v>
+        <v>3.599893232449097</v>
       </c>
       <c r="G47">
-        <v>-5.283297466245682</v>
+        <v>-6.773910321849005</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.970434786084449</v>
       </c>
       <c r="E48">
-        <v>-19.60769677135124</v>
+        <v>-22.83437941298461</v>
       </c>
       <c r="F48">
-        <v>2.66952066766886</v>
+        <v>3.29078462262485</v>
       </c>
       <c r="G48">
-        <v>-5.579220510910055</v>
+        <v>-7.050830835117962</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.113877675187302</v>
       </c>
       <c r="E49">
-        <v>-18.74673876453894</v>
+        <v>-22.04613964178749</v>
       </c>
       <c r="F49">
-        <v>2.575308786213667</v>
+        <v>3.419771367649567</v>
       </c>
       <c r="G49">
-        <v>-4.90106518882697</v>
+        <v>-7.537533998119454</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.248601835594252</v>
       </c>
       <c r="E50">
-        <v>-17.32084909679576</v>
+        <v>-21.10933875229473</v>
       </c>
       <c r="F50">
-        <v>2.901324374729052</v>
+        <v>3.347582461965201</v>
       </c>
       <c r="G50">
-        <v>-6.180296401202289</v>
+        <v>-7.168649840315084</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.373130048246853</v>
       </c>
       <c r="E51">
-        <v>-17.80926766089305</v>
+        <v>-20.7271083752033</v>
       </c>
       <c r="F51">
-        <v>3.120162475200625</v>
+        <v>3.920284206299473</v>
       </c>
       <c r="G51">
-        <v>-6.39800449695584</v>
+        <v>-8.070435824121477</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.48529869401775</v>
       </c>
       <c r="E52">
-        <v>-17.26187930826788</v>
+        <v>-19.31102738216074</v>
       </c>
       <c r="F52">
-        <v>2.922721104743363</v>
+        <v>3.737654045004266</v>
       </c>
       <c r="G52">
-        <v>-6.608230759790639</v>
+        <v>-8.742711617326815</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.582770146444088</v>
       </c>
       <c r="E53">
-        <v>-16.51865256870699</v>
+        <v>-17.55349492046582</v>
       </c>
       <c r="F53">
-        <v>2.903377069153189</v>
+        <v>3.420240223599551</v>
       </c>
       <c r="G53">
-        <v>-7.241491773815667</v>
+        <v>-8.650456644783945</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.664236996491701</v>
       </c>
       <c r="E54">
-        <v>-15.60719754823517</v>
+        <v>-19.00656448920304</v>
       </c>
       <c r="F54">
-        <v>2.677797714757633</v>
+        <v>3.998941004664897</v>
       </c>
       <c r="G54">
-        <v>-7.296708362865171</v>
+        <v>-8.21477229908816</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.729230415060095</v>
       </c>
       <c r="E55">
-        <v>-15.55392005153493</v>
+        <v>-17.29868674500222</v>
       </c>
       <c r="F55">
-        <v>3.277923390328985</v>
+        <v>3.795513851355006</v>
       </c>
       <c r="G55">
-        <v>-7.149614203464274</v>
+        <v>-9.728241161094612</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.777593147427429</v>
       </c>
       <c r="E56">
-        <v>-14.74745770093093</v>
+        <v>-16.87376644344049</v>
       </c>
       <c r="F56">
-        <v>3.196166841142285</v>
+        <v>4.182462489285516</v>
       </c>
       <c r="G56">
-        <v>-7.998312279002914</v>
+        <v>-9.459745986223101</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.810110641571705</v>
       </c>
       <c r="E57">
-        <v>-14.35167360113455</v>
+        <v>-17.81642717829917</v>
       </c>
       <c r="F57">
-        <v>3.319230759236985</v>
+        <v>4.167971029940942</v>
       </c>
       <c r="G57">
-        <v>-8.313737747439134</v>
+        <v>-9.313254346110352</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.827816196025285</v>
       </c>
       <c r="E58">
-        <v>-14.14330039814561</v>
+        <v>-16.42694191310365</v>
       </c>
       <c r="F58">
-        <v>3.133427950789056</v>
+        <v>3.675533116733525</v>
       </c>
       <c r="G58">
-        <v>-8.733945292738825</v>
+        <v>-10.12390432176615</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.833502832247541</v>
       </c>
       <c r="E59">
-        <v>-14.01842319891009</v>
+        <v>-15.76314913611132</v>
       </c>
       <c r="F59">
-        <v>3.022705050261263</v>
+        <v>3.655574432530474</v>
       </c>
       <c r="G59">
-        <v>-8.395554569896682</v>
+        <v>-9.94510506773565</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.829720756985989</v>
       </c>
       <c r="E60">
-        <v>-12.66771978511626</v>
+        <v>-15.47895569281195</v>
       </c>
       <c r="F60">
-        <v>3.093066577455053</v>
+        <v>3.729834256721839</v>
       </c>
       <c r="G60">
-        <v>-8.912363834032307</v>
+        <v>-10.55550014372093</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.820316087062246</v>
       </c>
       <c r="E61">
-        <v>-12.5594666139629</v>
+        <v>-14.84514141375039</v>
       </c>
       <c r="F61">
-        <v>3.15747379975752</v>
+        <v>3.74874257105814</v>
       </c>
       <c r="G61">
-        <v>-9.424690619507759</v>
+        <v>-10.28222785163625</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.807206435014637</v>
       </c>
       <c r="E62">
-        <v>-12.37659777658516</v>
+        <v>-13.24492361060793</v>
       </c>
       <c r="F62">
-        <v>3.098334994136858</v>
+        <v>3.540562245590985</v>
       </c>
       <c r="G62">
-        <v>-10.17215883354656</v>
+        <v>-9.979849243170301</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.792829188686187</v>
       </c>
       <c r="E63">
-        <v>-13.35062272242097</v>
+        <v>-13.03110265338776</v>
       </c>
       <c r="F63">
-        <v>3.095488723740839</v>
+        <v>3.761978225420071</v>
       </c>
       <c r="G63">
-        <v>-9.808912534795573</v>
+        <v>-10.97513165409679</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.77663231588803</v>
       </c>
       <c r="E64">
-        <v>-11.32664390706274</v>
+        <v>-13.71062734908274</v>
       </c>
       <c r="F64">
-        <v>2.89516629145664</v>
+        <v>3.363906270004768</v>
       </c>
       <c r="G64">
-        <v>-10.75554978956801</v>
+        <v>-11.09199060108753</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.759247843415234</v>
       </c>
       <c r="E65">
-        <v>-11.33445552472597</v>
+        <v>-14.08889983989146</v>
       </c>
       <c r="F65">
-        <v>2.344588583716337</v>
+        <v>3.474650708085034</v>
       </c>
       <c r="G65">
-        <v>-10.30668616208039</v>
+        <v>-11.10798384658774</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.738717291797997</v>
       </c>
       <c r="E66">
-        <v>-9.850379494458233</v>
+        <v>-13.57910687847797</v>
       </c>
       <c r="F66">
-        <v>2.42653234393607</v>
+        <v>3.072693709550602</v>
       </c>
       <c r="G66">
-        <v>-9.70463035030853</v>
+        <v>-11.24991355494738</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.71536195880504</v>
       </c>
       <c r="E67">
-        <v>-10.8290415976779</v>
+        <v>-12.37460524802178</v>
       </c>
       <c r="F67">
-        <v>2.667093551178658</v>
+        <v>3.260184730765436</v>
       </c>
       <c r="G67">
-        <v>-10.01830454015447</v>
+        <v>-11.20470805560863</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.686942466740902</v>
       </c>
       <c r="E68">
-        <v>-9.786487254684012</v>
+        <v>-12.26870688335241</v>
       </c>
       <c r="F68">
-        <v>2.627398185236505</v>
+        <v>3.264573421265468</v>
       </c>
       <c r="G68">
-        <v>-10.59385612433893</v>
+        <v>-11.98430511410606</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.653237322480062</v>
       </c>
       <c r="E69">
-        <v>-10.16332874770631</v>
+        <v>-13.93349619737024</v>
       </c>
       <c r="F69">
-        <v>1.977035340154974</v>
+        <v>3.058450760426867</v>
       </c>
       <c r="G69">
-        <v>-10.434367282439</v>
+        <v>-12.15059050599812</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.610653676572062</v>
       </c>
       <c r="E70">
-        <v>-10.23825687863722</v>
+        <v>-12.50743444761477</v>
       </c>
       <c r="F70">
-        <v>2.264911236710664</v>
+        <v>3.297086841825349</v>
       </c>
       <c r="G70">
-        <v>-10.80258271004444</v>
+        <v>-11.07660980651207</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.557392254547216</v>
       </c>
       <c r="E71">
-        <v>-11.39934402878188</v>
+        <v>-12.16773096992938</v>
       </c>
       <c r="F71">
-        <v>1.961200268883059</v>
+        <v>2.655297599362793</v>
       </c>
       <c r="G71">
-        <v>-10.91634629695595</v>
+        <v>-10.52379835963687</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.488373991242469</v>
       </c>
       <c r="E72">
-        <v>-10.68811095808519</v>
+        <v>-13.14157930527889</v>
       </c>
       <c r="F72">
-        <v>2.054898562548517</v>
+        <v>2.699787555832349</v>
       </c>
       <c r="G72">
-        <v>-10.60795904833622</v>
+        <v>-10.74575719586285</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.400901023458658</v>
       </c>
       <c r="E73">
-        <v>-10.64275829089837</v>
+        <v>-13.41138125818188</v>
       </c>
       <c r="F73">
-        <v>1.801512571175787</v>
+        <v>2.663128984788859</v>
       </c>
       <c r="G73">
-        <v>-10.30741117155349</v>
+        <v>-10.82689866703038</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.290132002783725</v>
       </c>
       <c r="E74">
-        <v>-10.67756867059533</v>
+        <v>-13.66788308292434</v>
       </c>
       <c r="F74">
-        <v>1.748397653308283</v>
+        <v>2.511839275811169</v>
       </c>
       <c r="G74">
-        <v>-10.66813152405802</v>
+        <v>-10.54569761837915</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.154165384222036</v>
       </c>
       <c r="E75">
-        <v>-10.97232704375459</v>
+        <v>-13.89295276957957</v>
       </c>
       <c r="F75">
-        <v>1.738606350607193</v>
+        <v>2.978299587266793</v>
       </c>
       <c r="G75">
-        <v>-9.761042046297712</v>
+        <v>-10.73660022690122</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.990097128057633</v>
       </c>
       <c r="E76">
-        <v>-10.93241307385099</v>
+        <v>-12.84679828974959</v>
       </c>
       <c r="F76">
-        <v>1.915421372734747</v>
+        <v>2.368099307342593</v>
       </c>
       <c r="G76">
-        <v>-9.811299438129387</v>
+        <v>-10.79729245827268</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.798103245340874</v>
       </c>
       <c r="E77">
-        <v>-11.45887534808671</v>
+        <v>-14.734510793743</v>
       </c>
       <c r="F77">
-        <v>1.44888319474326</v>
+        <v>2.17347769952446</v>
       </c>
       <c r="G77">
-        <v>-9.899068621466546</v>
+        <v>-9.70676565218136</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.578026707478835</v>
       </c>
       <c r="E78">
-        <v>-12.05535688742904</v>
+        <v>-12.88948368574589</v>
       </c>
       <c r="F78">
-        <v>1.451146294487708</v>
+        <v>1.99786215339616</v>
       </c>
       <c r="G78">
-        <v>-9.55864191311775</v>
+        <v>-10.02140983187031</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.33200634177739</v>
       </c>
       <c r="E79">
-        <v>-12.3776257401849</v>
+        <v>-13.70332292050837</v>
       </c>
       <c r="F79">
-        <v>1.682766103984478</v>
+        <v>2.191502974209377</v>
       </c>
       <c r="G79">
-        <v>-8.528479594389498</v>
+        <v>-9.823929169361707</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.061976538288774</v>
       </c>
       <c r="E80">
-        <v>-13.84333427987752</v>
+        <v>-14.31601639679816</v>
       </c>
       <c r="F80">
-        <v>0.9820020726470138</v>
+        <v>2.082138596222176</v>
       </c>
       <c r="G80">
-        <v>-9.200046930849433</v>
+        <v>-9.238366495466497</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.7718442635271393</v>
       </c>
       <c r="E81">
-        <v>-13.81199723974444</v>
+        <v>-15.37282184749418</v>
       </c>
       <c r="F81">
-        <v>1.259712244435548</v>
+        <v>2.041497234706026</v>
       </c>
       <c r="G81">
-        <v>-8.424409284816969</v>
+        <v>-10.0649666795305</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.4664075951953752</v>
       </c>
       <c r="E82">
-        <v>-13.92173575037232</v>
+        <v>-15.50124937035171</v>
       </c>
       <c r="F82">
-        <v>1.54348772234738</v>
+        <v>2.11589291115145</v>
       </c>
       <c r="G82">
-        <v>-8.017536616949462</v>
+        <v>-9.16163798150281</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.151679644015845</v>
       </c>
       <c r="E83">
-        <v>-14.61331977234973</v>
+        <v>-16.93780359438296</v>
       </c>
       <c r="F83">
-        <v>1.31092688748103</v>
+        <v>2.073289975625471</v>
       </c>
       <c r="G83">
-        <v>-7.904680119515707</v>
+        <v>-8.239985413915251</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.1657712568114268</v>
       </c>
       <c r="E84">
-        <v>-15.31298259195682</v>
+        <v>-16.95906930832298</v>
       </c>
       <c r="F84">
-        <v>1.303668732297701</v>
+        <v>1.750220061594442</v>
       </c>
       <c r="G84">
-        <v>-8.353841696101865</v>
+        <v>-8.141566205578258</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.481019149524254</v>
       </c>
       <c r="E85">
-        <v>-16.07183256684417</v>
+        <v>-18.06868129442244</v>
       </c>
       <c r="F85">
-        <v>1.051175720985189</v>
+        <v>1.747405269159729</v>
       </c>
       <c r="G85">
-        <v>-7.319915287095463</v>
+        <v>-8.110039880407777</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.7903781448232535</v>
       </c>
       <c r="E86">
-        <v>-17.88249761407108</v>
+        <v>-18.88703541777058</v>
       </c>
       <c r="F86">
-        <v>0.7968984062870474</v>
+        <v>1.686427487904852</v>
       </c>
       <c r="G86">
-        <v>-6.853730885346373</v>
+        <v>-7.737822003245361</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.092642070355314</v>
       </c>
       <c r="E87">
-        <v>-18.57289970433249</v>
+        <v>-20.28890153090306</v>
       </c>
       <c r="F87">
-        <v>1.170830078849967</v>
+        <v>1.187054482801198</v>
       </c>
       <c r="G87">
-        <v>-7.281804286847373</v>
+        <v>-7.8639206828362</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.385097261926119</v>
       </c>
       <c r="E88">
-        <v>-18.85274128411049</v>
+        <v>-20.15253559311009</v>
       </c>
       <c r="F88">
-        <v>1.064858693744632</v>
+        <v>1.059966355863698</v>
       </c>
       <c r="G88">
-        <v>-6.992803592905616</v>
+        <v>-7.548392587488264</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.665353111218577</v>
       </c>
       <c r="E89">
-        <v>-20.91447398727066</v>
+        <v>-22.7098010930336</v>
       </c>
       <c r="F89">
-        <v>0.9576099661041795</v>
+        <v>1.090534769761805</v>
       </c>
       <c r="G89">
-        <v>-6.980415531497663</v>
+        <v>-7.537918021402009</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.927740732564148</v>
       </c>
       <c r="E90">
-        <v>-22.77248423024777</v>
+        <v>-23.30190812648452</v>
       </c>
       <c r="F90">
-        <v>0.7254749120828685</v>
+        <v>1.223472827297875</v>
       </c>
       <c r="G90">
-        <v>-6.757480084337602</v>
+        <v>-7.705769301334137</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.166247372833678</v>
       </c>
       <c r="E91">
-        <v>-24.46614709453851</v>
+        <v>-24.69742984753226</v>
       </c>
       <c r="F91">
-        <v>0.6057360607430056</v>
+        <v>0.8396603883543635</v>
       </c>
       <c r="G91">
-        <v>-6.656932195218858</v>
+        <v>-7.733514983498769</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.371629664467906</v>
       </c>
       <c r="E92">
-        <v>-25.12047083238081</v>
+        <v>-26.25442789474551</v>
       </c>
       <c r="F92">
-        <v>0.7591049719017228</v>
+        <v>0.9616523990298411</v>
       </c>
       <c r="G92">
-        <v>-6.039167844863158</v>
+        <v>-7.480036443193392</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.53500328672432</v>
       </c>
       <c r="E93">
-        <v>-27.46564525215508</v>
+        <v>-28.06875194897063</v>
       </c>
       <c r="F93">
-        <v>0.2292298222921854</v>
+        <v>0.4187478585416703</v>
       </c>
       <c r="G93">
-        <v>-6.324007183062051</v>
+        <v>-7.207386533670096</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.645419429420984</v>
       </c>
       <c r="E94">
-        <v>-28.74587655344154</v>
+        <v>-29.58770628604544</v>
       </c>
       <c r="F94">
-        <v>0.09883650941751526</v>
+        <v>0.6255804302444705</v>
       </c>
       <c r="G94">
-        <v>-5.877742333822756</v>
+        <v>-7.169146422145975</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.697005506866366</v>
       </c>
       <c r="E95">
-        <v>-30.72942062438528</v>
+        <v>-31.36015554112162</v>
       </c>
       <c r="F95">
-        <v>0.04830775458155102</v>
+        <v>0.1605813588873848</v>
       </c>
       <c r="G95">
-        <v>-6.699783896679184</v>
+        <v>-7.782299182565469</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.677770565010065</v>
       </c>
       <c r="E96">
-        <v>-33.01361461317227</v>
+        <v>-34.99623713965544</v>
       </c>
       <c r="F96">
-        <v>-0.09259919736945049</v>
+        <v>-0.3732517301727286</v>
       </c>
       <c r="G96">
-        <v>-6.083995942010429</v>
+        <v>-7.233010156144055</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.591707100609189</v>
       </c>
       <c r="E97">
-        <v>-35.08408047845623</v>
+        <v>-36.18102405851924</v>
       </c>
       <c r="F97">
-        <v>-0.7143502323582867</v>
+        <v>-0.5530223671934716</v>
       </c>
       <c r="G97">
-        <v>-6.868333701720098</v>
+        <v>-7.336424977699808</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.422833904396215</v>
       </c>
       <c r="E98">
-        <v>-37.07812608062376</v>
+        <v>-38.21824186763889</v>
       </c>
       <c r="F98">
-        <v>-0.7676772122809076</v>
+        <v>-0.3896219267868524</v>
       </c>
       <c r="G98">
-        <v>-6.688246645474824</v>
+        <v>-7.242964966580644</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.193712785643091</v>
       </c>
       <c r="E99">
-        <v>-41.03166502828029</v>
+        <v>-40.54252643681578</v>
       </c>
       <c r="F99">
-        <v>-0.7104088602557665</v>
+        <v>-1.433342488394354</v>
       </c>
       <c r="G99">
-        <v>-6.622754123071422</v>
+        <v>-7.702554761615505</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.8757813979316</v>
       </c>
       <c r="E100">
-        <v>-42.65053788009735</v>
+        <v>-43.09311923028899</v>
       </c>
       <c r="F100">
-        <v>-1.182528577807317</v>
+        <v>-1.304936428919</v>
       </c>
       <c r="G100">
-        <v>-7.209041806439732</v>
+        <v>-8.462629533067856</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.527247467506576</v>
       </c>
       <c r="E101">
-        <v>-43.37242192166008</v>
+        <v>-44.24447242555416</v>
       </c>
       <c r="F101">
-        <v>-1.470936286235604</v>
+        <v>-1.868111948121077</v>
       </c>
       <c r="G101">
-        <v>-6.838810256600878</v>
+        <v>-7.6467985536431</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.070291282478435</v>
       </c>
       <c r="E102">
-        <v>-47.0517844105222</v>
+        <v>-46.89069300464735</v>
       </c>
       <c r="F102">
-        <v>-1.304005343958253</v>
+        <v>-1.902086608779496</v>
       </c>
       <c r="G102">
-        <v>-7.899658021932633</v>
+        <v>-8.085929177245266</v>
       </c>
     </row>
   </sheetData>
